--- a/practice-files/day12-图表.xlsx
+++ b/practice-files/day12-图表.xlsx
@@ -8,9 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="练习说明" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月度统计" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类统计" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月度统计" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类统计" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -566,19 +565,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -807,7 +793,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/practice-files/day12-图表.xlsx
+++ b/practice-files/day12-图表.xlsx
@@ -516,7 +516,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   （右键图表→更改图表类型→组合）</t>
+          <t xml:space="preserve">   （右键图表→更改图表类型→组合。WPS更直接：插入→全部图表→组合图，量级差太多记得给折线勾"次坐标轴"）</t>
         </is>
       </c>
     </row>

--- a/practice-files/day12-图表.xlsx
+++ b/practice-files/day12-图表.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -34,6 +34,22 @@
     </font>
     <font>
       <name val="微软雅黑"/>
+      <sz val="10.5"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <color rgb="00E67E22"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <sz val="10.5"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <color rgb="002E7D32"/>
       <sz val="10.5"/>
     </font>
     <font>
@@ -87,16 +103,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -462,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -551,6 +572,41 @@
       <c r="A15" s="2" t="inlineStr">
         <is>
           <t>【美化】给每张图加上标题、数据标签，调整颜色。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>📝 思考题（先自己想想，点左侧+号展开答案）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>思考题1: 折线图和柱状图各适合什么场景？</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" hidden="1" outlineLevel="1">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>💡 答案: 折线图=展示随时间的变化趋势；柱状图=分类之间比大小。分类数据画成折线图会暗示"连续性"，误导读者。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>思考题2: 饼图分类超过几个就不该用？</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" hidden="1" outlineLevel="1">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>💡 答案: 5个。分类太多饼图碎成一片，读者分不清谁大谁小，改用柱状图。</t>
         </is>
       </c>
     </row>
@@ -575,216 +631,216 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>月份</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>销售额（万元）</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>订单数</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>客单价（元）</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>1月</t>
         </is>
       </c>
-      <c r="B2" s="4" t="n">
+      <c r="B2" s="7" t="n">
         <v>85.59999999999999</v>
       </c>
-      <c r="C2" s="4" t="n">
+      <c r="C2" s="7" t="n">
         <v>2140</v>
       </c>
-      <c r="D2" s="4" t="n">
+      <c r="D2" s="7" t="n">
         <v>400</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>2月</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n">
+      <c r="B3" s="7" t="n">
         <v>62.3</v>
       </c>
-      <c r="C3" s="4" t="n">
+      <c r="C3" s="7" t="n">
         <v>1558</v>
       </c>
-      <c r="D3" s="4" t="n">
+      <c r="D3" s="7" t="n">
         <v>400</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>3月</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n">
+      <c r="B4" s="7" t="n">
         <v>98.7</v>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="C4" s="7" t="n">
         <v>2320</v>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D4" s="7" t="n">
         <v>425</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>4月</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B5" s="7" t="n">
         <v>105.2</v>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="C5" s="7" t="n">
         <v>2391</v>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" s="7" t="n">
         <v>440</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>5月</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B6" s="7" t="n">
         <v>92.09999999999999</v>
       </c>
-      <c r="C6" s="4" t="n">
+      <c r="C6" s="7" t="n">
         <v>2193</v>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D6" s="7" t="n">
         <v>420</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>6月</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="B7" s="7" t="n">
         <v>118.5</v>
       </c>
-      <c r="C7" s="4" t="n">
+      <c r="C7" s="7" t="n">
         <v>2633</v>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="D7" s="7" t="n">
         <v>450</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>7月</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n">
+      <c r="B8" s="7" t="n">
         <v>132.8</v>
       </c>
-      <c r="C8" s="4" t="n">
+      <c r="C8" s="7" t="n">
         <v>2951</v>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="D8" s="7" t="n">
         <v>450</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>8月</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n">
+      <c r="B9" s="7" t="n">
         <v>125.4</v>
       </c>
-      <c r="C9" s="4" t="n">
+      <c r="C9" s="7" t="n">
         <v>2726</v>
       </c>
-      <c r="D9" s="4" t="n">
+      <c r="D9" s="7" t="n">
         <v>460</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>9月</t>
         </is>
       </c>
-      <c r="B10" s="4" t="n">
+      <c r="B10" s="7" t="n">
         <v>108.9</v>
       </c>
-      <c r="C10" s="4" t="n">
+      <c r="C10" s="7" t="n">
         <v>2475</v>
       </c>
-      <c r="D10" s="4" t="n">
+      <c r="D10" s="7" t="n">
         <v>440</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>10月</t>
         </is>
       </c>
-      <c r="B11" s="4" t="n">
+      <c r="B11" s="7" t="n">
         <v>145.3</v>
       </c>
-      <c r="C11" s="4" t="n">
+      <c r="C11" s="7" t="n">
         <v>3125</v>
       </c>
-      <c r="D11" s="4" t="n">
+      <c r="D11" s="7" t="n">
         <v>465</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>11月</t>
         </is>
       </c>
-      <c r="B12" s="4" t="n">
+      <c r="B12" s="7" t="n">
         <v>168.7</v>
       </c>
-      <c r="C12" s="4" t="n">
+      <c r="C12" s="7" t="n">
         <v>3515</v>
       </c>
-      <c r="D12" s="4" t="n">
+      <c r="D12" s="7" t="n">
         <v>480</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>12月</t>
         </is>
       </c>
-      <c r="B13" s="4" t="n">
+      <c r="B13" s="7" t="n">
         <v>189.2</v>
       </c>
-      <c r="C13" s="4" t="n">
+      <c r="C13" s="7" t="n">
         <v>3784</v>
       </c>
-      <c r="D13" s="4" t="n">
+      <c r="D13" s="7" t="n">
         <v>500</v>
       </c>
     </row>
@@ -808,92 +864,92 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>分类</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>销售额（万元）</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>占比</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>电子产品</t>
         </is>
       </c>
-      <c r="B2" s="4" t="n">
+      <c r="B2" s="7" t="n">
         <v>420.5</v>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>33.1%</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>服装鞋帽</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n">
+      <c r="B3" s="7" t="n">
         <v>288.3</v>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="7" t="inlineStr">
         <is>
           <t>22.7%</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>家居用品</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n">
+      <c r="B4" s="7" t="n">
         <v>215.7</v>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>17.0%</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>食品饮料</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B5" s="7" t="n">
         <v>186.2</v>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>14.7%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>运动户外</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B6" s="7" t="n">
         <v>158.6</v>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>12.5%</t>
         </is>

--- a/practice-files/day12-图表.xlsx
+++ b/practice-files/day12-图表.xlsx
@@ -578,7 +578,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>📝 思考题（先自己想想，点左侧+号展开答案）</t>
+          <t>思考题（先自己想想，点左侧+号展开答案）</t>
         </is>
       </c>
     </row>
@@ -592,7 +592,7 @@
     <row r="19" hidden="1" outlineLevel="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>💡 答案: 折线图=展示随时间的变化趋势；柱状图=分类之间比大小。分类数据画成折线图会暗示"连续性"，误导读者。</t>
+          <t>答案: 折线图=展示随时间的变化趋势；柱状图=分类之间比大小。分类数据画成折线图会暗示"连续性"，误导读者。</t>
         </is>
       </c>
     </row>
@@ -606,7 +606,7 @@
     <row r="22" hidden="1" outlineLevel="1">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>💡 答案: 5个。分类太多饼图碎成一片，读者分不清谁大谁小，改用柱状图。</t>
+          <t>答案: 5个。分类太多饼图碎成一片，读者分不清谁大谁小，改用柱状图。</t>
         </is>
       </c>
     </row>
